--- a/results/Faculty-Course-Assignments-AY-2026-2027_v1.xlsx
+++ b/results/Faculty-Course-Assignments-AY-2026-2027_v1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeffreyvarner/Desktop/julia_work/department-codes/Teaching-Matching-Problem-CBE/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4EB3A5B1-D4D6-1F4B-8D9C-A253CC18EE54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{DC9765BB-174E-E84A-AE34-3EFBACE09EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3260" yWindow="2260" windowWidth="28040" windowHeight="17180" xr2:uid="{47C35A1F-B684-8E4F-AD88-57F2B41FECE3}"/>
+    <workbookView xWindow="460" yWindow="1640" windowWidth="31260" windowHeight="17720" xr2:uid="{1DFF37BD-BE22-C449-97AE-738A654FD32D}"/>
   </bookViews>
   <sheets>
     <sheet name="Faculty-Course-Assignments-AY-2" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="123">
   <si>
     <t>Faculty</t>
   </si>
@@ -55,12 +55,21 @@
     <t>Total_Credits</t>
   </si>
   <si>
+    <t>Total_Credits_Undiluted</t>
+  </si>
+  <si>
     <t>Abbott</t>
   </si>
   <si>
     <t>Alabi</t>
   </si>
   <si>
+    <t>CHEME-4320</t>
+  </si>
+  <si>
+    <t>Chemical Engineering Laboratory</t>
+  </si>
+  <si>
     <t>CHEME-4620; CHEME-6430</t>
   </si>
   <si>
@@ -73,10 +82,16 @@
     <t>Bauer</t>
   </si>
   <si>
-    <t>CHEME-4320; CHEME-5020; CHEME-5650</t>
-  </si>
-  <si>
-    <t>Chemical Engineering Laboratory; Immersive Professional Development for Chemical Engineering M. Eng.; Design Project</t>
+    <t>CHEME-4320; CHEME-5020; CHEME-5650; CHEME-5651; CHEME-6660</t>
+  </si>
+  <si>
+    <t>Chemical Engineering Laboratory; Immersive Professional Development for Chemical Engineering M. Eng.; Design Project; M. Eng. Design Project Studio; Analysis of Sustainable Energy Systems</t>
+  </si>
+  <si>
+    <t>CHEME-4620; CHEME-5650; CHEME-5651</t>
+  </si>
+  <si>
+    <t>Chemical Engineering Design; Design Project; M. Eng. Design Project Studio</t>
   </si>
   <si>
     <t>Cardenas</t>
@@ -91,16 +106,16 @@
     <t>Celik</t>
   </si>
   <si>
-    <t>CHEME-4320; CHEME-5020</t>
-  </si>
-  <si>
-    <t>Chemical Engineering Laboratory; Immersive Professional Development for Chemical Engineering M. Eng.</t>
-  </si>
-  <si>
-    <t>CHEME-5240; CHEME-5460; CHEME-5650</t>
-  </si>
-  <si>
-    <t>Chemical Process Safety Management; Introduction to Synthetic Biology; Design Project</t>
+    <t>CHEME-5020; CHEME-5990</t>
+  </si>
+  <si>
+    <t>Immersive Professional Development for Chemical Engineering M. Eng.; Medical and Industrial Biotechnology Seminar</t>
+  </si>
+  <si>
+    <t>CHEME-5460; CHEME-5650; CHEME-5990</t>
+  </si>
+  <si>
+    <t>Introduction to Synthetic Biology; Design Project; Medical and Industrial Biotechnology Seminar</t>
   </si>
   <si>
     <t>Cleary</t>
@@ -112,12 +127,15 @@
     <t>Principles in Process and Lean Engineering</t>
   </si>
   <si>
+    <t>CHEME-5240</t>
+  </si>
+  <si>
+    <t>Chemical Process Safety Management</t>
+  </si>
+  <si>
     <t>Coso-Strong</t>
   </si>
   <si>
-    <t>Principles of Computational Thinking for Engineers</t>
-  </si>
-  <si>
     <t>CHEME-3720; CHEME-4620</t>
   </si>
   <si>
@@ -136,10 +154,10 @@
     <t>DeLisa</t>
   </si>
   <si>
-    <t>CHEME-2880; CHEME-4320; ENGRI-1120</t>
-  </si>
-  <si>
-    <t>Biomolecular Engineering: Fundamentals and Applications; Chemical Engineering Laboratory; Feast! Chemical and Biomolecular Processes and Products through Food</t>
+    <t>CHEME-2880; ENGRI-1120</t>
+  </si>
+  <si>
+    <t>Biomolecular Engineering: Fundamentals and Applications; Feast! Chemical and Biomolecular Processes and Products through Food</t>
   </si>
   <si>
     <t>CHEME-4620; CHEME-5430</t>
@@ -169,16 +187,16 @@
     <t>Escobedo</t>
   </si>
   <si>
-    <t>CHEME-6110</t>
-  </si>
-  <si>
-    <t>Mathematical Methods of Chemical Engineering Analysis</t>
-  </si>
-  <si>
-    <t>CHEME-5540</t>
-  </si>
-  <si>
-    <t>Principles of Molecular Simulation</t>
+    <t>CHEME-4320; CHEME-6110</t>
+  </si>
+  <si>
+    <t>Chemical Engineering Laboratory; Mathematical Methods of Chemical Engineering Analysis</t>
+  </si>
+  <si>
+    <t>CHEME-4620; CHEME-5540</t>
+  </si>
+  <si>
+    <t>Chemical Engineering Design; Principles of Molecular Simulation</t>
   </si>
   <si>
     <t>Godwin</t>
@@ -205,19 +223,19 @@
     <t>Heat and Mass Transfer</t>
   </si>
   <si>
-    <t>CHEME-4410</t>
-  </si>
-  <si>
-    <t>Air Pollution Control</t>
+    <t>CHEME-4xxx</t>
+  </si>
+  <si>
+    <t>The AIChemeE of an Empire</t>
   </si>
   <si>
     <t>Hanrath</t>
   </si>
   <si>
-    <t>CHEME-6660; CHEME-6662; CHEME-6681</t>
-  </si>
-  <si>
-    <t>Analysis of Sustainable Energy Systems; Solar Energy Module; Energy Analysis Project</t>
+    <t>CHEME-5870; CHEME-6660; CHEME-6662; CHEME-6681</t>
+  </si>
+  <si>
+    <t>Energy Seminar I; Analysis of Sustainable Energy Systems; Solar Energy Module; Energy Analysis Project</t>
   </si>
   <si>
     <t>Harimoto</t>
@@ -262,28 +280,25 @@
     <t>Kowal</t>
   </si>
   <si>
-    <t>CHEME-5651; CHEME-6920; ENGRD-2190</t>
-  </si>
-  <si>
-    <t>M. Eng. Design Project Studio; Principles and Practices of Graduate Research; Chemical Process Design and Analysis</t>
-  </si>
-  <si>
-    <t>CHEME-4020; CHEME-4620</t>
-  </si>
-  <si>
-    <t>Molecular Principles of Biomedical Engineering; Chemical Engineering Design</t>
+    <t>CHEME-4320; CHEME-6920; ENGRD-2190</t>
+  </si>
+  <si>
+    <t>Chemical Engineering Laboratory; Principles and Practices of Graduate Research; Chemical Process Design and Analysis</t>
+  </si>
+  <si>
+    <t>CHEME-4620</t>
+  </si>
+  <si>
+    <t>Chemical Engineering Design</t>
   </si>
   <si>
     <t>Li</t>
   </si>
   <si>
-    <t>Chemical Engineering Laboratory</t>
-  </si>
-  <si>
-    <t>CHEME-5440</t>
-  </si>
-  <si>
-    <t>Kinetics and Dynamics in Molecular and Cellular Systems</t>
+    <t>CHEME-5999</t>
+  </si>
+  <si>
+    <t>Special Projects in Chemical Engineering</t>
   </si>
   <si>
     <t>Putnam</t>
@@ -316,24 +331,21 @@
     <t>Varner</t>
   </si>
   <si>
-    <t>CHEME-4800; CHEME-5660</t>
-  </si>
-  <si>
-    <t>Principles of Computational Thinking for Engineers; Financial Data, Markets, and Mayhem for Scientists and Engineers</t>
-  </si>
-  <si>
-    <t>CHEME-5650; CHEME-5820</t>
-  </si>
-  <si>
-    <t>Design Project; Machine Learning and Artificial Intelligence Methods for Engineers</t>
+    <t>CHEME-5020; CHEME-5660; CHEME-5800</t>
+  </si>
+  <si>
+    <t>Immersive Professional Development for Chemical Engineering M. Eng.; Financial Data, Markets, and Mayhem for Scientists and Engineers; Principles of Computational Thinking for Engineers</t>
+  </si>
+  <si>
+    <t>CHEME-4620; CHEME-5650; CHEME-5820</t>
+  </si>
+  <si>
+    <t>Chemical Engineering Design; Design Project; Machine Learning and Artificial Intelligence Methods for Engineers</t>
   </si>
   <si>
     <t>Yang</t>
   </si>
   <si>
-    <t>Medical and Industrial Biotechnology Seminar</t>
-  </si>
-  <si>
     <t>CHEME-6400</t>
   </si>
   <si>
@@ -377,22 +389,13 @@
   </si>
   <si>
     <t>Analysis of Separation Processes</t>
-  </si>
-  <si>
-    <t>TBD (systems course?)</t>
-  </si>
-  <si>
-    <t>TBD (5999 development of new bio course)</t>
-  </si>
-  <si>
-    <t>TBD (5999 development of new semiconductor course)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -527,8 +530,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -706,6 +716,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -875,12 +891,27 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1255,56 +1286,66 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{791964F5-DB94-3545-8B33-6C673E69301E}">
-  <dimension ref="A1:K32"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E112F969-D05B-EC4D-B4F4-F8B2505DC8AA}">
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="54.33203125" customWidth="1"/>
-    <col min="3" max="3" width="44.1640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="29.6640625" customWidth="1"/>
-    <col min="5" max="5" width="48.83203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="25" style="3" customWidth="1"/>
+    <col min="3" max="3" width="25.6640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="28.1640625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="40.33203125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="8" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="15.83203125" customWidth="1"/>
+    <col min="9" max="9" width="17.33203125" customWidth="1"/>
+    <col min="10" max="10" width="22.5" customWidth="1"/>
+    <col min="11" max="11" width="22.6640625" customWidth="1"/>
+    <col min="12" max="12" width="23.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+    <row r="1" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2" s="6" t="s">
+        <v>12</v>
+      </c>
       <c r="F2">
         <v>0</v>
       </c>
@@ -1323,39 +1364,51 @@
       <c r="K2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" ht="34" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="L2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3">
         <v>2</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>3.5714285714285698</v>
       </c>
       <c r="K3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>15</v>
+        <v>4.5714285714285703</v>
+      </c>
+      <c r="L3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" s="6" t="s">
+        <v>18</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -1375,45 +1428,57 @@
       <c r="K4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" ht="51" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="L4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="119" x14ac:dyDescent="0.2">
+      <c r="A5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>8</v>
+      </c>
+      <c r="I5">
+        <v>5.5</v>
+      </c>
+      <c r="J5">
+        <v>1.9047619047619</v>
+      </c>
+      <c r="K5">
+        <v>7.4047619047618998</v>
+      </c>
+      <c r="L5">
         <v>18</v>
       </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
-      <c r="I5">
-        <v>3.5</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="17" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>21</v>
+    </row>
+    <row r="6" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1433,22 +1498,25 @@
       <c r="K6">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" ht="51" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>26</v>
+      <c r="L6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="A7" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="F7">
         <v>2</v>
@@ -1460,88 +1528,99 @@
         <v>5</v>
       </c>
       <c r="I7">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J7">
-        <v>3.5</v>
+        <v>2.3333333333333299</v>
       </c>
       <c r="K7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="17" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>29</v>
+        <v>4.3333333333333304</v>
+      </c>
+      <c r="L7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A8" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>36</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8">
         <v>3</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="34" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
+      </c>
+      <c r="L8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A9" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>39</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9">
         <v>2</v>
       </c>
       <c r="H9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>3</v>
+        <v>2.5714285714285698</v>
       </c>
       <c r="K9">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="17" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>36</v>
+        <v>2.5714285714285698</v>
+      </c>
+      <c r="L9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A10" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1561,45 +1640,51 @@
       <c r="K10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" ht="68" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>41</v>
+      <c r="L10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="A11" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G11">
         <v>2</v>
       </c>
       <c r="H11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I11">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="J11">
-        <v>4</v>
+        <v>3.5714285714285698</v>
       </c>
       <c r="K11">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>42</v>
+        <v>9.0714285714285694</v>
+      </c>
+      <c r="L11">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1619,22 +1704,25 @@
       <c r="K12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" ht="17" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B13" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" t="s">
-        <v>46</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>47</v>
+      <c r="L12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A13" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>53</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -1654,57 +1742,63 @@
       <c r="K13">
         <v>6</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" ht="34" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B14" t="s">
-        <v>49</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" t="s">
-        <v>51</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>52</v>
+      <c r="L13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="A14" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J14">
-        <v>3</v>
+        <v>3.5714285714285698</v>
       </c>
       <c r="K14">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="34" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>53</v>
-      </c>
-      <c r="B15" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D15" t="s">
-        <v>56</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>57</v>
+        <v>7.5714285714285703</v>
+      </c>
+      <c r="L14">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="A15" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -1724,22 +1818,25 @@
       <c r="K15">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" ht="17" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>58</v>
-      </c>
-      <c r="B16" t="s">
-        <v>59</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D16" t="s">
-        <v>61</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>62</v>
+      <c r="L15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A16" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>68</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -1759,39 +1856,45 @@
       <c r="K16">
         <v>7</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" ht="34" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>63</v>
-      </c>
-      <c r="B17" t="s">
-        <v>64</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>65</v>
+      <c r="L16">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="A17" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>71</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G17">
         <v>0</v>
       </c>
       <c r="H17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I17">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="J17">
         <v>0</v>
       </c>
       <c r="K17">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>66</v>
+        <v>4.5</v>
+      </c>
+      <c r="L17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A18" s="6" t="s">
+        <v>72</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1811,16 +1914,19 @@
       <c r="K18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" ht="17" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>67</v>
-      </c>
-      <c r="D19" t="s">
-        <v>68</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>69</v>
+      <c r="L18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A19" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>75</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1840,10 +1946,13 @@
       <c r="K19">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>70</v>
+      <c r="L19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A20" s="6" t="s">
+        <v>76</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1863,16 +1972,19 @@
       <c r="K20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" ht="17" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>71</v>
-      </c>
-      <c r="B21" t="s">
-        <v>72</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>73</v>
+      <c r="L20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A21" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>79</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -1892,22 +2004,25 @@
       <c r="K21">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" ht="17" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>74</v>
-      </c>
-      <c r="B22" t="s">
-        <v>75</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D22" t="s">
-        <v>77</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>78</v>
+      <c r="L21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A22" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>84</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -1927,86 +2042,91 @@
       <c r="K22">
         <v>6</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" ht="51" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>79</v>
-      </c>
-      <c r="B23" t="s">
-        <v>80</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D23" t="s">
-        <v>82</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>83</v>
+      <c r="L22">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="A23" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="F23">
         <v>3</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I23">
         <v>6</v>
       </c>
       <c r="J23">
-        <v>4</v>
+        <v>0.57142857142857095</v>
       </c>
       <c r="K23">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="17" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>84</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D24" t="s">
-        <v>86</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>87</v>
-      </c>
+        <v>6.5714285714285703</v>
+      </c>
+      <c r="L23">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A24" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
       <c r="F24">
         <v>1</v>
       </c>
       <c r="G24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I24">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J24">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K24">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="17" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>88</v>
-      </c>
-      <c r="B25" t="s">
-        <v>89</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>90</v>
+        <v>0.5</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A25" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -2026,22 +2146,25 @@
       <c r="K25">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" ht="34" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>91</v>
-      </c>
-      <c r="B26" t="s">
-        <v>92</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D26" t="s">
-        <v>94</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>95</v>
+      <c r="L25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="A26" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>100</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -2061,10 +2184,13 @@
       <c r="K26">
         <v>7</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>96</v>
+      <c r="L26">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A27" s="6" t="s">
+        <v>101</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -2084,57 +2210,63 @@
       <c r="K27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" ht="51" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>97</v>
-      </c>
-      <c r="B28" t="s">
-        <v>98</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="D28" t="s">
-        <v>100</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>101</v>
+      <c r="L27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="119" x14ac:dyDescent="0.2">
+      <c r="A28" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>106</v>
       </c>
       <c r="F28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J28">
-        <v>4.5</v>
+        <v>4.9047619047618998</v>
       </c>
       <c r="K28">
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="17" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>102</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D29" t="s">
-        <v>104</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>105</v>
+        <v>12.9047619047619</v>
+      </c>
+      <c r="L28">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A29" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>109</v>
       </c>
       <c r="F29">
         <v>1</v>
@@ -2146,30 +2278,33 @@
         <v>2</v>
       </c>
       <c r="I29">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J29">
         <v>3</v>
       </c>
       <c r="K29">
+        <v>3.5</v>
+      </c>
+      <c r="L29">
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="34" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>106</v>
-      </c>
-      <c r="B30" t="s">
-        <v>107</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="D30" t="s">
-        <v>109</v>
-      </c>
-      <c r="E30" s="1" t="s">
+    <row r="30" spans="1:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="A30" s="6" t="s">
         <v>110</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>114</v>
       </c>
       <c r="F30">
         <v>4</v>
@@ -2189,16 +2324,19 @@
       <c r="K30">
         <v>16</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" ht="17" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>111</v>
-      </c>
-      <c r="B31" t="s">
-        <v>112</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>113</v>
+      <c r="L30">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A31" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>117</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -2218,22 +2356,25 @@
       <c r="K31">
         <v>4</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" ht="17" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>114</v>
-      </c>
-      <c r="B32" t="s">
-        <v>115</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="D32" t="s">
-        <v>117</v>
-      </c>
-      <c r="E32" s="1" t="s">
+      <c r="L31">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A32" s="6" t="s">
         <v>118</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>122</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -2251,6 +2392,9 @@
         <v>4</v>
       </c>
       <c r="K32">
+        <v>7</v>
+      </c>
+      <c r="L32">
         <v>7</v>
       </c>
     </row>
